--- a/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/gpt-4o-mini/headline/headline.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/gpt-4o-mini/headline/headline.xlsx
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4.042</v>
+        <v>4.229</v>
       </c>
       <c r="E5" t="n">
-        <v>3.464</v>
+        <v>3.543</v>
       </c>
       <c r="F5" t="n">
-        <v>2.908</v>
+        <v>2.935</v>
       </c>
       <c r="G5" t="n">
-        <v>3.559</v>
+        <v>3.682</v>
       </c>
       <c r="H5" t="n">
-        <v>4.01</v>
+        <v>4.25</v>
       </c>
       <c r="I5" t="n">
-        <v>0.578</v>
+        <v>0.625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.34</v>
+        <v>0.281</v>
       </c>
       <c r="K5" t="n">
-        <v>0.713</v>
+        <v>0.79</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>0.324</v>
       </c>
       <c r="M5" t="n">
-        <v>0.539</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="6">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>4.12</v>
+        <v>4.229</v>
       </c>
       <c r="E9" t="n">
-        <v>3.441</v>
+        <v>3.543</v>
       </c>
       <c r="F9" t="n">
-        <v>2.921</v>
+        <v>2.935</v>
       </c>
       <c r="G9" t="n">
-        <v>3.622</v>
+        <v>3.682</v>
       </c>
       <c r="H9" t="n">
-        <v>4.083</v>
+        <v>4.25</v>
       </c>
       <c r="I9" t="n">
-        <v>0.614</v>
+        <v>0.625</v>
       </c>
       <c r="J9" t="n">
-        <v>0.305</v>
+        <v>0.281</v>
       </c>
       <c r="K9" t="n">
-        <v>0.696</v>
+        <v>0.79</v>
       </c>
       <c r="L9" t="n">
-        <v>0.342</v>
+        <v>0.324</v>
       </c>
       <c r="M9" t="n">
-        <v>0.624</v>
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>

--- a/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/gpt-4o-mini/headline/headline.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/outcomes/tables/gpt-4o-mini/headline/headline.xlsx
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4.229</v>
+        <v>4.517</v>
       </c>
       <c r="E5" t="n">
-        <v>3.543</v>
+        <v>3.729</v>
       </c>
       <c r="F5" t="n">
-        <v>2.935</v>
+        <v>3.062</v>
       </c>
       <c r="G5" t="n">
-        <v>3.682</v>
+        <v>3.832</v>
       </c>
       <c r="H5" t="n">
-        <v>4.25</v>
+        <v>4.536</v>
       </c>
       <c r="I5" t="n">
-        <v>0.625</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.281</v>
+        <v>0.21</v>
       </c>
       <c r="K5" t="n">
-        <v>0.79</v>
+        <v>1.114</v>
       </c>
       <c r="L5" t="n">
-        <v>0.324</v>
+        <v>0.41</v>
       </c>
       <c r="M5" t="n">
-        <v>0.625</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="6">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>4.229</v>
+        <v>4.517</v>
       </c>
       <c r="E9" t="n">
-        <v>3.543</v>
+        <v>3.729</v>
       </c>
       <c r="F9" t="n">
-        <v>2.935</v>
+        <v>3.062</v>
       </c>
       <c r="G9" t="n">
-        <v>3.682</v>
+        <v>3.832</v>
       </c>
       <c r="H9" t="n">
-        <v>4.25</v>
+        <v>4.536</v>
       </c>
       <c r="I9" t="n">
-        <v>0.625</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.281</v>
+        <v>0.21</v>
       </c>
       <c r="K9" t="n">
-        <v>0.79</v>
+        <v>1.114</v>
       </c>
       <c r="L9" t="n">
-        <v>0.324</v>
+        <v>0.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0.625</v>
+        <v>0.707</v>
       </c>
     </row>
   </sheetData>
